--- a/products/Schedule Risk & Contingency Starter Kit.xlsx
+++ b/products/Schedule Risk & Contingency Starter Kit.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Risk Register" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Risk Register'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +94,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0033415C"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -143,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,6 +202,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,6 +565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0014213D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -659,10 +669,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1254,11 +1265,21 @@
         <v/>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>CPM Toolkit  |  Schedule Risk &amp; Contingency Starter Kit  |  v1.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>